--- a/Predictions/2026-05-09.xlsx
+++ b/Predictions/2026-05-09.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gdsak\OneDrive\Desktop\Glicko-2, Etc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gdsak\OneDrive\Desktop\Glicko-2, Etc\Predictions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECBE2121-AB0C-4AF2-A4FB-BD35450AE434}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E74AD4C2-6390-4966-ACA6-5E46D08EAE94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Predictions" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="48">
   <si>
     <t>Red Corner</t>
   </si>
@@ -161,6 +161,9 @@
   </si>
   <si>
     <t>Glicko-2</t>
+  </si>
+  <si>
+    <t>Model</t>
   </si>
 </sst>
 </file>
@@ -260,14 +263,14 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -589,10 +592,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="K1" s="4" t="s">
+      <c r="D1" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="L1" s="4"/>
+      <c r="L1" s="6"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -680,10 +692,10 @@
       <c r="C4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="5">
         <v>0.60747513320201174</v>
       </c>
       <c r="F4" s="2" t="s">
@@ -739,10 +751,10 @@
       <c r="J5" s="3">
         <v>0.13855913187769081</v>
       </c>
-      <c r="K5" s="5" t="s">
+      <c r="K5" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="L5" s="6">
+      <c r="L5" s="5">
         <v>0.55777453262137255</v>
       </c>
     </row>
@@ -756,10 +768,10 @@
       <c r="C6" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="5">
         <v>0.64028976373491375</v>
       </c>
       <c r="F6" s="2" t="s">
@@ -777,10 +789,10 @@
       <c r="J6" s="3">
         <v>0.4962501890797566</v>
       </c>
-      <c r="K6" s="5" t="s">
+      <c r="K6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="L6" s="6">
+      <c r="L6" s="5">
         <v>0.5581912571265758</v>
       </c>
     </row>
@@ -794,10 +806,10 @@
       <c r="C7" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="5">
         <v>0.74186958240330603</v>
       </c>
       <c r="F7" s="2" t="s">
@@ -815,10 +827,10 @@
       <c r="J7" s="3">
         <v>0.17646227895192071</v>
       </c>
-      <c r="K7" s="5" t="s">
+      <c r="K7" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L7" s="6">
+      <c r="L7" s="5">
         <v>0.65351366081773088</v>
       </c>
     </row>
@@ -832,31 +844,31 @@
       <c r="C8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="5">
         <v>0.79366334035227604</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="5">
         <v>0.60897802803332057</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H8" s="5">
         <v>0.27753420022982028</v>
       </c>
-      <c r="I8" s="6">
+      <c r="I8" s="5">
         <v>0.60897802803332057</v>
       </c>
-      <c r="J8" s="6">
+      <c r="J8" s="5">
         <v>0.1134877717368592</v>
       </c>
-      <c r="K8" s="5" t="s">
+      <c r="K8" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="L8" s="6">
+      <c r="L8" s="5">
         <v>0.77792928459159383</v>
       </c>
     </row>
@@ -870,25 +882,25 @@
       <c r="C9" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="5">
         <v>0.54463272463344481</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="5">
         <v>0.58508190977866492</v>
       </c>
-      <c r="H9" s="6">
+      <c r="H9" s="5">
         <v>0.21382972198186179</v>
       </c>
-      <c r="I9" s="6">
+      <c r="I9" s="5">
         <v>0.20108836823947321</v>
       </c>
-      <c r="J9" s="6">
+      <c r="J9" s="5">
         <v>0.58508190977866492</v>
       </c>
       <c r="K9" s="2" t="s">
@@ -908,31 +920,31 @@
       <c r="C10" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="5">
         <v>0.69074549369927596</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G10" s="6">
+      <c r="G10" s="5">
         <v>0.46750055609344848</v>
       </c>
-      <c r="H10" s="6">
+      <c r="H10" s="5">
         <v>0.33158370611127302</v>
       </c>
-      <c r="I10" s="6">
+      <c r="I10" s="5">
         <v>0.20091573779527849</v>
       </c>
-      <c r="J10" s="6">
+      <c r="J10" s="5">
         <v>0.46750055609344848</v>
       </c>
-      <c r="K10" s="5" t="s">
+      <c r="K10" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L10" s="6">
+      <c r="L10" s="5">
         <v>0.69210860186915901</v>
       </c>
     </row>
@@ -967,10 +979,10 @@
       <c r="J11" s="3">
         <v>9.7122149008241968E-2</v>
       </c>
-      <c r="K11" s="5" t="s">
+      <c r="K11" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="L11" s="6">
+      <c r="L11" s="5">
         <v>0.57114585520007499</v>
       </c>
     </row>
@@ -1022,10 +1034,10 @@
       <c r="C13" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="5">
         <v>0.59537942101281749</v>
       </c>
       <c r="F13" s="2" t="s">
@@ -1043,10 +1055,10 @@
       <c r="J13" s="3">
         <v>0.43131335355988132</v>
       </c>
-      <c r="K13" s="5" t="s">
+      <c r="K13" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="L13" s="6">
+      <c r="L13" s="5">
         <v>0.56237910820502524</v>
       </c>
     </row>
@@ -1060,10 +1072,10 @@
       <c r="C14" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E14" s="5">
         <v>0.76434416649465198</v>
       </c>
       <c r="F14" s="2" t="s">
@@ -1081,10 +1093,10 @@
       <c r="J14" s="3">
         <v>0.23576042458968949</v>
       </c>
-      <c r="K14" s="5" t="s">
+      <c r="K14" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="L14" s="6">
+      <c r="L14" s="5">
         <v>0.64061261395633706</v>
       </c>
     </row>
@@ -1127,8 +1139,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="K1:L1"/>
+    <mergeCell ref="D1:J1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
